--- a/Team-Data/2012-13/2-8-2012-13.xlsx
+++ b/Team-Data/2012-13/2-8-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,40 +728,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
         <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.551</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J2" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.385</v>
+        <v>0.381</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="P2" t="n">
         <v>19.3</v>
@@ -703,19 +770,19 @@
         <v>0.701</v>
       </c>
       <c r="R2" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S2" t="n">
         <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U2" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
         <v>8</v>
@@ -727,22 +794,22 @@
         <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA2" t="n">
         <v>19</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
         <v>12</v>
@@ -757,10 +824,10 @@
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -793,10 +860,10 @@
         <v>3</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
@@ -805,7 +872,7 @@
         <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>24</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -945,7 +1012,7 @@
         <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM3" t="n">
         <v>28</v>
@@ -954,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>0.58</v>
+        <v>0.592</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>34.8</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="L4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M4" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O4" t="n">
         <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.743</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
@@ -1091,28 +1158,28 @@
         <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>95</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>9</v>
@@ -1124,10 +1191,10 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM4" t="n">
         <v>7</v>
@@ -1139,10 +1206,10 @@
         <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>9</v>
@@ -1154,13 +1221,13 @@
         <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>20</v>
@@ -1169,13 +1236,13 @@
         <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -1207,67 +1274,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.224</v>
+        <v>0.229</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
         <v>0.425</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
         <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R5" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S5" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T5" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U5" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="V5" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y5" t="n">
         <v>7.6</v>
@@ -1276,7 +1343,7 @@
         <v>19.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB5" t="n">
         <v>94.5</v>
@@ -1285,7 +1352,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1324,13 +1391,13 @@
         <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT5" t="n">
         <v>24</v>
@@ -1339,10 +1406,10 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6</v>
+        <v>0.592</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1410,37 +1477,37 @@
         <v>81.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L6" t="n">
         <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
         <v>17.4</v>
       </c>
       <c r="P6" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
         <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>43.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V6" t="n">
         <v>14.5</v>
@@ -1452,10 +1519,10 @@
         <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA6" t="n">
         <v>20.3</v>
@@ -1467,19 +1534,19 @@
         <v>1.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1497,28 +1564,28 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>7</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
@@ -1527,19 +1594,19 @@
         <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
         <v>12</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -1571,61 +1638,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
         <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>0.32</v>
+        <v>0.306</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J7" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L7" t="n">
         <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R7" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S7" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T7" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U7" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V7" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
         <v>8.1</v>
@@ -1637,25 +1704,25 @@
         <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1664,7 +1731,7 @@
         <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ7" t="n">
         <v>3</v>
@@ -1679,19 +1746,19 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
         <v>29</v>
@@ -1703,7 +1770,7 @@
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>12</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
@@ -1724,7 +1791,7 @@
         <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1846,7 +1913,7 @@
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>4</v>
@@ -1858,10 +1925,10 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>11</v>
@@ -1888,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2052,10 +2119,10 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
         <v>10</v>
@@ -2067,7 +2134,7 @@
         <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>5</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.373</v>
+        <v>0.36</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J10" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O10" t="n">
         <v>16.2</v>
       </c>
       <c r="P10" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.696</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R10" t="n">
         <v>12.8</v>
@@ -2165,10 +2232,10 @@
         <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2180,19 +2247,19 @@
         <v>5.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z10" t="n">
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.2</v>
+        <v>94.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
         <v>3</v>
@@ -2213,19 +2280,19 @@
         <v>19</v>
       </c>
       <c r="AJ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK10" t="n">
         <v>17</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>21</v>
@@ -2237,10 +2304,10 @@
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
         <v>5</v>
@@ -2267,10 +2334,10 @@
         <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.612</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J11" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L11" t="n">
         <v>7.8</v>
@@ -2332,25 +2399,25 @@
         <v>0.393</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.801</v>
+        <v>0.802</v>
       </c>
       <c r="R11" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
@@ -2365,22 +2432,22 @@
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA11" t="n">
         <v>19.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>7</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>8</v>
       </c>
       <c r="AK11" t="n">
         <v>9</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,7 +2486,7 @@
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2428,22 +2495,22 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
         <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
         <v>18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
         <v>23</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -2481,67 +2548,67 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.538</v>
+        <v>0.529</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J12" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L12" t="n">
         <v>10.3</v>
       </c>
       <c r="M12" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O12" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P12" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0.755</v>
       </c>
       <c r="R12" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
         <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
         <v>23</v>
       </c>
       <c r="V12" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>6.4</v>
@@ -2550,37 +2617,37 @@
         <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB12" t="n">
-        <v>106</v>
+        <v>105.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF12" t="n">
         <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>11</v>
       </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2601,7 +2668,7 @@
         <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2619,7 +2686,7 @@
         <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
         <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" t="n">
-        <v>0.608</v>
+        <v>0.62</v>
       </c>
       <c r="H13" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I13" t="n">
         <v>34.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L13" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
         <v>16.6</v>
       </c>
       <c r="P13" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R13" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
         <v>32.7</v>
       </c>
       <c r="T13" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V13" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
         <v>6.8</v>
@@ -2726,25 +2793,25 @@
         <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z13" t="n">
         <v>19.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>92.8</v>
+        <v>92.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
         <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,13 +2820,13 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
@@ -2771,16 +2838,16 @@
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
         <v>5</v>
@@ -2795,7 +2862,7 @@
         <v>25</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>26</v>
@@ -2807,7 +2874,7 @@
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E14" t="n">
         <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.673</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J14" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.47</v>
@@ -2875,13 +2942,13 @@
         <v>19.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O14" t="n">
         <v>16.9</v>
       </c>
       <c r="P14" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
         <v>0.706</v>
@@ -2890,16 +2957,16 @@
         <v>11.6</v>
       </c>
       <c r="S14" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T14" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U14" t="n">
         <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W14" t="n">
         <v>10.1</v>
@@ -2911,16 +2978,16 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
         <v>21.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2929,7 +2996,7 @@
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
         <v>4</v>
@@ -2953,13 +3020,13 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>26</v>
@@ -2974,10 +3041,10 @@
         <v>18</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2998,7 +3065,7 @@
         <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
         <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>0.471</v>
+        <v>0.46</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3057,28 +3124,28 @@
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P15" t="n">
         <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S15" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T15" t="n">
         <v>45</v>
       </c>
       <c r="U15" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3087,22 +3154,22 @@
         <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y15" t="n">
         <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA15" t="n">
         <v>22.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
         <v>3</v>
@@ -3123,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3144,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3159,13 +3226,13 @@
         <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
         <v>25</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.633</v>
+        <v>0.625</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,22 +3294,22 @@
         <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.436</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O16" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
         <v>20.3</v>
@@ -3254,43 +3321,43 @@
         <v>13.6</v>
       </c>
       <c r="S16" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T16" t="n">
         <v>42.9</v>
       </c>
       <c r="U16" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V16" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X16" t="n">
         <v>5.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="AC16" t="n">
         <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF16" t="n">
         <v>6</v>
@@ -3299,16 +3366,16 @@
         <v>7</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>9</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
@@ -3329,10 +3396,10 @@
         <v>5</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3341,22 +3408,22 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
         <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -3391,43 +3458,43 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="H17" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I17" t="n">
         <v>38.6</v>
       </c>
       <c r="J17" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.491</v>
+        <v>0.49</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.381</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.756</v>
@@ -3439,13 +3506,13 @@
         <v>30.4</v>
       </c>
       <c r="T17" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U17" t="n">
         <v>22.3</v>
       </c>
       <c r="V17" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W17" t="n">
         <v>8.300000000000001</v>
@@ -3454,7 +3521,7 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z17" t="n">
         <v>19.6</v>
@@ -3463,10 +3530,10 @@
         <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD17" t="n">
         <v>29</v>
@@ -3493,16 +3560,16 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM17" t="n">
         <v>9</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3526,7 +3593,7 @@
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>18</v>
@@ -3544,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3696,10 +3763,10 @@
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" t="n">
-        <v>0.383</v>
+        <v>0.391</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,19 +3840,19 @@
         <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.436</v>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0.299</v>
+        <v>0.302</v>
       </c>
       <c r="O19" t="n">
         <v>18.5</v>
@@ -3797,7 +3864,7 @@
         <v>0.731</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S19" t="n">
         <v>30.5</v>
@@ -3806,16 +3873,16 @@
         <v>43.6</v>
       </c>
       <c r="U19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y19" t="n">
         <v>6</v>
@@ -3830,16 +3897,16 @@
         <v>95.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
         <v>21</v>
@@ -3854,10 +3921,10 @@
         <v>16</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM19" t="n">
         <v>22</v>
@@ -3872,22 +3939,22 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU19" t="n">
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>15</v>
@@ -3899,7 +3966,7 @@
         <v>23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -3937,52 +4004,52 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
       </c>
       <c r="G20" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J20" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L20" t="n">
         <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.373</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P20" t="n">
         <v>19.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
         <v>11.2</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
         <v>41.1</v>
@@ -4003,31 +4070,31 @@
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>93.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF20" t="n">
         <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
@@ -4051,7 +4118,7 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
@@ -4060,7 +4127,7 @@
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
         <v>22</v>
@@ -4069,13 +4136,13 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
         <v>23</v>
@@ -4087,10 +4154,10 @@
         <v>25</v>
       </c>
       <c r="BB20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC20" t="n">
         <v>25</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.667</v>
+        <v>0.66</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4137,19 +4204,19 @@
         <v>37</v>
       </c>
       <c r="J21" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L21" t="n">
         <v>11.2</v>
       </c>
       <c r="M21" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O21" t="n">
         <v>15.6</v>
@@ -4158,31 +4225,31 @@
         <v>20.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
         <v>41</v>
       </c>
       <c r="U21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V21" t="n">
         <v>11.5</v>
       </c>
       <c r="W21" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y21" t="n">
         <v>3.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.7</v>
       </c>
       <c r="Z21" t="n">
         <v>18.9</v>
@@ -4197,10 +4264,10 @@
         <v>5.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
         <v>4</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4248,13 +4315,13 @@
         <v>23</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4263,7 +4330,7 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -4301,67 +4368,67 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.76</v>
+        <v>0.755</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
       </c>
       <c r="I22" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="J22" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="L22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M22" t="n">
         <v>19.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.389</v>
+        <v>0.383</v>
       </c>
       <c r="O22" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="P22" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.831</v>
+        <v>0.833</v>
       </c>
       <c r="R22" t="n">
         <v>10.4</v>
       </c>
       <c r="S22" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T22" t="n">
         <v>43.3</v>
       </c>
       <c r="U22" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="Y22" t="n">
         <v>4.1</v>
@@ -4373,19 +4440,19 @@
         <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.6</v>
+        <v>106.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>2</v>
@@ -4394,7 +4461,7 @@
         <v>9</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>28</v>
@@ -4409,7 +4476,7 @@
         <v>13</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,7 +4494,7 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>17</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.28</v>
+        <v>0.286</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J23" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L23" t="n">
         <v>6.7</v>
@@ -4513,7 +4580,7 @@
         <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O23" t="n">
         <v>12.3</v>
@@ -4528,13 +4595,13 @@
         <v>10.6</v>
       </c>
       <c r="S23" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V23" t="n">
         <v>14.7</v>
@@ -4543,34 +4610,34 @@
         <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5</v>
+        <v>-4.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH23" t="n">
         <v>22</v>
@@ -4579,16 +4646,16 @@
         <v>10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>17</v>
       </c>
       <c r="AM23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN23" t="n">
         <v>24</v>
@@ -4612,10 +4679,10 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -4767,13 +4834,13 @@
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4797,13 +4864,13 @@
         <v>14</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" t="n">
         <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4868,7 +4935,7 @@
         <v>83.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
@@ -4877,13 +4944,13 @@
         <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="O25" t="n">
         <v>15</v>
       </c>
       <c r="P25" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.754</v>
@@ -4892,49 +4959,49 @@
         <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T25" t="n">
         <v>40.6</v>
       </c>
       <c r="U25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V25" t="n">
         <v>14.4</v>
       </c>
       <c r="W25" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X25" t="n">
         <v>5.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
         <v>18.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.8</v>
+        <v>-4.3</v>
       </c>
       <c r="AD25" t="n">
         <v>3</v>
       </c>
       <c r="AE25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF25" t="n">
         <v>24</v>
       </c>
-      <c r="AF25" t="n">
-        <v>26</v>
-      </c>
       <c r="AG25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -4946,7 +5013,7 @@
         <v>6</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>26</v>
@@ -4970,7 +5037,7 @@
         <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT25" t="n">
         <v>25</v>
@@ -4979,28 +5046,28 @@
         <v>18</v>
       </c>
       <c r="AV25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H26" t="n">
         <v>48.7</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
         <v>0.441</v>
@@ -5056,25 +5123,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P26" t="n">
         <v>21.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R26" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S26" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T26" t="n">
         <v>42</v>
@@ -5083,7 +5150,7 @@
         <v>21.2</v>
       </c>
       <c r="V26" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W26" t="n">
         <v>7.2</v>
@@ -5092,28 +5159,28 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
         <v>19.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.1</v>
+        <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
         <v>17</v>
@@ -5122,25 +5189,25 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
         <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>19</v>
@@ -5155,34 +5222,34 @@
         <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV26" t="n">
         <v>21</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5301,10 +5368,10 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>10</v>
@@ -5319,13 +5386,13 @@
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO27" t="n">
         <v>15</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>18</v>
@@ -5337,19 +5404,19 @@
         <v>30</v>
       </c>
       <c r="AT27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU27" t="n">
         <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
         <v>10</v>
       </c>
       <c r="AX27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E28" t="n">
         <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.765</v>
+        <v>0.78</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5420,40 +5487,40 @@
         <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N28" t="n">
         <v>0.38</v>
       </c>
       <c r="O28" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P28" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R28" t="n">
         <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T28" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y28" t="n">
         <v>4.6</v>
@@ -5465,10 +5532,10 @@
         <v>18.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AD28" t="n">
         <v>3</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,10 +5571,10 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW28" t="n">
         <v>3</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -5575,40 +5642,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.36</v>
+        <v>0.347</v>
       </c>
       <c r="H29" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.5</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
         <v>0.442</v>
       </c>
       <c r="L29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O29" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P29" t="n">
         <v>22.2</v>
@@ -5617,31 +5684,31 @@
         <v>0.772</v>
       </c>
       <c r="R29" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
         <v>29.2</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
         <v>19.5</v>
@@ -5650,13 +5717,13 @@
         <v>97.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>22</v>
@@ -5680,49 +5747,49 @@
         <v>11</v>
       </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN29" t="n">
         <v>22</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT29" t="n">
         <v>28</v>
       </c>
-      <c r="AT29" t="n">
-        <v>27</v>
-      </c>
       <c r="AU29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>13</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E30" t="n">
         <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.549</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,61 +5842,61 @@
         <v>36.7</v>
       </c>
       <c r="J30" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O30" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P30" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U30" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X30" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z30" t="n">
         <v>21.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>97.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC30" t="n">
         <v>-0.5</v>
@@ -5853,25 +5920,25 @@
         <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
@@ -5880,31 +5947,31 @@
         <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
         <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.286</v>
+        <v>0.271</v>
       </c>
       <c r="H31" t="n">
         <v>48.7</v>
@@ -5966,25 +6033,25 @@
         <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="O31" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="P31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
         <v>43.3</v>
@@ -5996,7 +6063,7 @@
         <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
@@ -6005,28 +6072,28 @@
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-4.1</v>
+        <v>-4.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF31" t="n">
         <v>28</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6056,16 +6123,16 @@
         <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU31" t="n">
         <v>20</v>
@@ -6083,7 +6150,7 @@
         <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -6092,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-8-2012-13</t>
+          <t>2013-02-08</t>
         </is>
       </c>
     </row>
